--- a/data/OVTech Master Curriculum.xlsx
+++ b/data/OVTech Master Curriculum.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="23040" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Master Curriculum" sheetId="1" r:id="rId1"/>
@@ -1091,6 +1091,141 @@
     <t>https://youtu.be/G4k7ikIPWFc</t>
   </si>
   <si>
+    <t>Power Query</t>
+  </si>
+  <si>
+    <t>PQ-RES001</t>
+  </si>
+  <si>
+    <t>films</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>PQ-RES002</t>
+  </si>
+  <si>
+    <t>movie_ratings</t>
+  </si>
+  <si>
+    <t>PQ003</t>
+  </si>
+  <si>
+    <t>Introduction to Power Query</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9bht65Qv9Q0</t>
+  </si>
+  <si>
+    <t>PQ004</t>
+  </si>
+  <si>
+    <t>Accessing Power Query</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OfzMv4csB4M</t>
+  </si>
+  <si>
+    <t>PQ005</t>
+  </si>
+  <si>
+    <t>Reduce Rows Section</t>
+  </si>
+  <si>
+    <t>https://youtu.be/St8pQ6rkJ5Y</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>PQ006</t>
+  </si>
+  <si>
+    <t>Manage Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7d6h1stqUVI</t>
+  </si>
+  <si>
+    <t>PQ007</t>
+  </si>
+  <si>
+    <t>Conditional Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IIzoiGgQh9M</t>
+  </si>
+  <si>
+    <t>PQ008</t>
+  </si>
+  <si>
+    <t>Creating Index Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/u4vHsVY6iWg</t>
+  </si>
+  <si>
+    <t>PQ009</t>
+  </si>
+  <si>
+    <t>Power Query Home Tab</t>
+  </si>
+  <si>
+    <t>https://youtu.be/y-g2-xv1wi4</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>PQ010</t>
+  </si>
+  <si>
+    <t>Power Query Transform Tab</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GPCDungCTK8</t>
+  </si>
+  <si>
+    <t>PQ011</t>
+  </si>
+  <si>
+    <t>Close and Load</t>
+  </si>
+  <si>
+    <t>https://youtu.be/o1QVywo65fU</t>
+  </si>
+  <si>
+    <t>PQ012</t>
+  </si>
+  <si>
+    <t>External Data Source (Web)</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PEovlMLfN4</t>
+  </si>
+  <si>
+    <t>PQ013</t>
+  </si>
+  <si>
+    <t>Merging Queries Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/53qoq8gTmEw</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>PQ014</t>
+  </si>
+  <si>
+    <t>Merging Queries Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/rs1O1Q0AZrU</t>
+  </si>
+  <si>
     <t>Excel Final Project</t>
   </si>
   <si>
@@ -1166,9 +1301,6 @@
     <t>https://youtu.be/0HlrW6M_Y_A</t>
   </si>
   <si>
-    <t>2026-08-11</t>
-  </si>
-  <si>
     <t>EX097</t>
   </si>
   <si>
@@ -1176,138 +1308,6 @@
   </si>
   <si>
     <t>https://youtu.be/KqqP9gCVt3k</t>
-  </si>
-  <si>
-    <t>Power Query</t>
-  </si>
-  <si>
-    <t>PQ-RES001</t>
-  </si>
-  <si>
-    <t>films</t>
-  </si>
-  <si>
-    <t>PQ-RES002</t>
-  </si>
-  <si>
-    <t>movie_ratings</t>
-  </si>
-  <si>
-    <t>PQ003</t>
-  </si>
-  <si>
-    <t>Introduction to Power Query</t>
-  </si>
-  <si>
-    <t>https://youtu.be/9bht65Qv9Q0</t>
-  </si>
-  <si>
-    <t>PQ004</t>
-  </si>
-  <si>
-    <t>Accessing Power Query</t>
-  </si>
-  <si>
-    <t>https://youtu.be/OfzMv4csB4M</t>
-  </si>
-  <si>
-    <t>PQ005</t>
-  </si>
-  <si>
-    <t>Reduce Rows Section</t>
-  </si>
-  <si>
-    <t>https://youtu.be/St8pQ6rkJ5Y</t>
-  </si>
-  <si>
-    <t>2026-08-12</t>
-  </si>
-  <si>
-    <t>PQ006</t>
-  </si>
-  <si>
-    <t>Manage Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/7d6h1stqUVI</t>
-  </si>
-  <si>
-    <t>PQ007</t>
-  </si>
-  <si>
-    <t>Conditional Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/IIzoiGgQh9M</t>
-  </si>
-  <si>
-    <t>PQ008</t>
-  </si>
-  <si>
-    <t>Creating Index Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/u4vHsVY6iWg</t>
-  </si>
-  <si>
-    <t>PQ009</t>
-  </si>
-  <si>
-    <t>Power Query Home Tab</t>
-  </si>
-  <si>
-    <t>https://youtu.be/y-g2-xv1wi4</t>
-  </si>
-  <si>
-    <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>PQ010</t>
-  </si>
-  <si>
-    <t>Power Query Transform Tab</t>
-  </si>
-  <si>
-    <t>https://youtu.be/GPCDungCTK8</t>
-  </si>
-  <si>
-    <t>PQ011</t>
-  </si>
-  <si>
-    <t>Close and Load</t>
-  </si>
-  <si>
-    <t>https://youtu.be/o1QVywo65fU</t>
-  </si>
-  <si>
-    <t>PQ012</t>
-  </si>
-  <si>
-    <t>External Data Source (Web)</t>
-  </si>
-  <si>
-    <t>https://youtu.be/7PEovlMLfN4</t>
-  </si>
-  <si>
-    <t>PQ013</t>
-  </si>
-  <si>
-    <t>Merging Queries Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/53qoq8gTmEw</t>
-  </si>
-  <si>
-    <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>PQ014</t>
-  </si>
-  <si>
-    <t>Merging Queries Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/rs1O1Q0AZrU</t>
   </si>
   <si>
     <t>Power BI</t>
@@ -8040,7 +8040,7 @@
         <v>104</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>353</v>
@@ -8049,7 +8049,7 @@
         <v>354</v>
       </c>
       <c r="E105" s="5">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>16</v>
@@ -8064,16 +8064,16 @@
         <v>175</v>
       </c>
       <c r="J105" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K105" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L105" s="6" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="N105" s="6" t="s">
         <v>22</v>
@@ -8084,40 +8084,40 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E106" s="5">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>16</v>
       </c>
       <c r="G106" s="5" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="H106" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>132</v>
+        <v>175</v>
       </c>
       <c r="J106" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K106" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L106" s="6" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="N106" s="6" t="s">
         <v>22</v>
@@ -8128,40 +8128,40 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E107" s="5">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G107" s="5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="H107" s="5" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="I107" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J107" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K107" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L107" s="6" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="N107" s="6" t="s">
         <v>18</v>
@@ -8172,40 +8172,40 @@
         <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E108" s="5">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G108" s="5" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="H108" s="5" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J108" s="5">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K108" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L108" s="6" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="N108" s="6" t="s">
         <v>18</v>
@@ -8216,40 +8216,40 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E109" s="5">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G109" s="5" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="H109" s="5" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I109" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J109" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K109" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="N109" s="6" t="s">
         <v>18</v>
@@ -8260,40 +8260,40 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C110" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E110" s="5">
-        <v>93</v>
+        <v>6</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="H110" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J110" s="5">
+        <v>27</v>
+      </c>
+      <c r="K110" s="5">
+        <v>6</v>
+      </c>
+      <c r="L110" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I110" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J110" s="5">
-        <v>25</v>
-      </c>
-      <c r="K110" s="5">
-        <v>5</v>
-      </c>
-      <c r="L110" s="6" t="s">
-        <v>365</v>
-      </c>
       <c r="M110" s="6" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="N110" s="6" t="s">
         <v>18</v>
@@ -8304,40 +8304,40 @@
         <v>110</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C111" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E111" s="5">
-        <v>94</v>
+        <v>7</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G111" s="5" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="H111" s="5" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="I111" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J111" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K111" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="N111" s="6" t="s">
         <v>18</v>
@@ -8348,40 +8348,40 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C112" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E112" s="5">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H112" s="5" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="I112" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J112" s="5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K112" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="N112" s="6" t="s">
         <v>18</v>
@@ -8392,40 +8392,40 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C113" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E113" s="5">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H113" s="5" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="I113" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J113" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K113" s="5">
         <v>6</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="N113" s="6" t="s">
         <v>18</v>
@@ -8436,40 +8436,40 @@
         <v>113</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>353</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="E114" s="5">
-        <v>97</v>
+        <v>10</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="H114" s="5" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="I114" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J114" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K114" s="5">
         <v>6</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="N114" s="6" t="s">
         <v>18</v>
@@ -8480,43 +8480,43 @@
         <v>114</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E115" s="5">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="H115" s="5" t="s">
-        <v>18</v>
+        <v>387</v>
       </c>
       <c r="I115" s="5" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="J115" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K115" s="5">
         <v>6</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="N115" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -8524,43 +8524,43 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E116" s="5">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="H116" s="5" t="s">
-        <v>18</v>
+        <v>390</v>
       </c>
       <c r="I116" s="5" t="s">
-        <v>175</v>
+        <v>18</v>
       </c>
       <c r="J116" s="5">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K116" s="5">
         <v>6</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -8568,40 +8568,40 @@
         <v>116</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E117" s="5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="H117" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="I117" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J117" s="5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K117" s="5">
         <v>6</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="N117" s="6" t="s">
         <v>18</v>
@@ -8612,40 +8612,40 @@
         <v>117</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E118" s="5">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="H118" s="5" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="I118" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J118" s="5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K118" s="5">
         <v>6</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="N118" s="6" t="s">
         <v>18</v>
@@ -8656,43 +8656,43 @@
         <v>118</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E119" s="5">
+        <v>88</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G119" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="H119" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I119" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="J119" s="5">
+        <v>24</v>
+      </c>
+      <c r="K119" s="5">
         <v>5</v>
       </c>
-      <c r="F119" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="H119" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="I119" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J119" s="5">
-        <v>27</v>
-      </c>
-      <c r="K119" s="5">
-        <v>6</v>
-      </c>
       <c r="L119" s="6" t="s">
-        <v>396</v>
+        <v>349</v>
       </c>
       <c r="M119" s="6" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="N119" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="1:14">
@@ -8700,43 +8700,43 @@
         <v>119</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E120" s="5">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>398</v>
       </c>
       <c r="H120" s="5" t="s">
-        <v>399</v>
+        <v>18</v>
       </c>
       <c r="I120" s="5" t="s">
-        <v>18</v>
+        <v>132</v>
       </c>
       <c r="J120" s="5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K120" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>396</v>
+        <v>349</v>
       </c>
       <c r="M120" s="6" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="1:14">
@@ -8744,40 +8744,40 @@
         <v>120</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E121" s="5">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H121" s="5" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="I121" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J121" s="5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K121" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>396</v>
+        <v>349</v>
       </c>
       <c r="M121" s="6" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="N121" s="6" t="s">
         <v>18</v>
@@ -8788,40 +8788,40 @@
         <v>121</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D122" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="E122" s="5">
+        <v>91</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G122" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="E122" s="5">
-        <v>8</v>
-      </c>
-      <c r="F122" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G122" s="5" t="s">
-        <v>404</v>
-      </c>
       <c r="H122" s="5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="I122" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J122" s="5">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K122" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>396</v>
+        <v>349</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="N122" s="6" t="s">
         <v>18</v>
@@ -8832,40 +8832,40 @@
         <v>122</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E123" s="5">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H123" s="5" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J123" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K123" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M123" s="6" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="N123" s="6" t="s">
         <v>18</v>
@@ -8876,40 +8876,40 @@
         <v>123</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D124" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="E124" s="5">
+        <v>93</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G124" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="H124" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="I124" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J124" s="5">
+        <v>25</v>
+      </c>
+      <c r="K124" s="5">
+        <v>5</v>
+      </c>
+      <c r="L124" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="E124" s="5">
-        <v>10</v>
-      </c>
-      <c r="F124" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G124" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="H124" s="5" t="s">
-        <v>412</v>
-      </c>
-      <c r="I124" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J124" s="5">
-        <v>28</v>
-      </c>
-      <c r="K124" s="5">
-        <v>6</v>
-      </c>
-      <c r="L124" s="6" t="s">
-        <v>409</v>
-      </c>
       <c r="M124" s="6" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="N124" s="6" t="s">
         <v>18</v>
@@ -8920,40 +8920,40 @@
         <v>124</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E125" s="5">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="I125" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J125" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K125" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L125" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M125" s="6" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="N125" s="6" t="s">
         <v>18</v>
@@ -8964,40 +8964,40 @@
         <v>125</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E126" s="5">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H126" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I126" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J126" s="5">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K126" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="N126" s="6" t="s">
         <v>18</v>
@@ -9008,40 +9008,40 @@
         <v>126</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E127" s="5">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H127" s="5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="I127" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J127" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K127" s="5">
         <v>6</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>422</v>
+        <v>356</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="N127" s="6" t="s">
         <v>18</v>
@@ -9052,16 +9052,16 @@
         <v>127</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>382</v>
+        <v>75</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>423</v>
       </c>
       <c r="E128" s="5">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>24</v>
@@ -9076,16 +9076,16 @@
         <v>18</v>
       </c>
       <c r="J128" s="5">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K128" s="5">
         <v>6</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>422</v>
+        <v>356</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="N128" s="6" t="s">
         <v>18</v>
@@ -9126,7 +9126,7 @@
         <v>6</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="M129" s="6" t="s">
         <v>68</v>
@@ -9170,7 +9170,7 @@
         <v>6</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>422</v>
+        <v>394</v>
       </c>
       <c r="M130" s="6" t="s">
         <v>68</v>
@@ -11091,7 +11091,7 @@
         <v>16</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="H174" s="5" t="s">
         <v>18</v>
@@ -11135,7 +11135,7 @@
         <v>16</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="H175" s="5" t="s">
         <v>18</v>
@@ -13317,7 +13317,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F2:F224">
+    <dataValidation type="list" sqref="F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F2:F104 F119:F128 F129:F224">
       <formula1>"Video,Resource"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13738,16 +13738,16 @@
         <v>768</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>357</v>
+        <v>402</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>359</v>
+        <v>404</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>771</v>
@@ -13758,16 +13758,16 @@
         <v>768</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>358</v>
+        <v>403</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>361</v>
+        <v>406</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>772</v>

--- a/data/OVTech Master Curriculum.xlsx
+++ b/data/OVTech Master Curriculum.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2328" uniqueCount="773">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2325" uniqueCount="772">
   <si>
     <t>Global Order</t>
   </si>
@@ -431,13 +431,13 @@
     <t>Word Document</t>
   </si>
   <si>
-    <t>EX-RES018</t>
+    <t>EX018</t>
   </si>
   <si>
     <t>Excel Practical Teaching With Example</t>
   </si>
   <si>
-    <t>Video/Practice</t>
+    <t>https://www.youtube.com/watch?v=cKWal1lewQI</t>
   </si>
   <si>
     <t>EX019</t>
@@ -449,6 +449,9 @@
     <t>https://youtu.be/5QboNYn29sk</t>
   </si>
   <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
     <t>EX020</t>
   </si>
   <si>
@@ -458,9 +461,6 @@
     <t>https://youtu.be/L5pP5ORhHtA</t>
   </si>
   <si>
-    <t>2026-07-17</t>
-  </si>
-  <si>
     <t>EX021</t>
   </si>
   <si>
@@ -1100,189 +1100,189 @@
     <t>films</t>
   </si>
   <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>PQ-RES002</t>
+  </si>
+  <si>
+    <t>movie_ratings</t>
+  </si>
+  <si>
+    <t>PQ003</t>
+  </si>
+  <si>
+    <t>Introduction to Power Query</t>
+  </si>
+  <si>
+    <t>https://youtu.be/9bht65Qv9Q0</t>
+  </si>
+  <si>
+    <t>PQ004</t>
+  </si>
+  <si>
+    <t>Accessing Power Query</t>
+  </si>
+  <si>
+    <t>https://youtu.be/OfzMv4csB4M</t>
+  </si>
+  <si>
+    <t>PQ005</t>
+  </si>
+  <si>
+    <t>Reduce Rows Section</t>
+  </si>
+  <si>
+    <t>https://youtu.be/St8pQ6rkJ5Y</t>
+  </si>
+  <si>
+    <t>PQ006</t>
+  </si>
+  <si>
+    <t>Manage Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7d6h1stqUVI</t>
+  </si>
+  <si>
+    <t>PQ007</t>
+  </si>
+  <si>
+    <t>Conditional Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/IIzoiGgQh9M</t>
+  </si>
+  <si>
     <t>2026-08-11</t>
   </si>
   <si>
-    <t>PQ-RES002</t>
-  </si>
-  <si>
-    <t>movie_ratings</t>
-  </si>
-  <si>
-    <t>PQ003</t>
-  </si>
-  <si>
-    <t>Introduction to Power Query</t>
-  </si>
-  <si>
-    <t>https://youtu.be/9bht65Qv9Q0</t>
-  </si>
-  <si>
-    <t>PQ004</t>
-  </si>
-  <si>
-    <t>Accessing Power Query</t>
-  </si>
-  <si>
-    <t>https://youtu.be/OfzMv4csB4M</t>
-  </si>
-  <si>
-    <t>PQ005</t>
-  </si>
-  <si>
-    <t>Reduce Rows Section</t>
-  </si>
-  <si>
-    <t>https://youtu.be/St8pQ6rkJ5Y</t>
+    <t>PQ008</t>
+  </si>
+  <si>
+    <t>Creating Index Columns</t>
+  </si>
+  <si>
+    <t>https://youtu.be/u4vHsVY6iWg</t>
+  </si>
+  <si>
+    <t>PQ009</t>
+  </si>
+  <si>
+    <t>Power Query Home Tab</t>
+  </si>
+  <si>
+    <t>https://youtu.be/y-g2-xv1wi4</t>
+  </si>
+  <si>
+    <t>PQ010</t>
+  </si>
+  <si>
+    <t>Power Query Transform Tab</t>
+  </si>
+  <si>
+    <t>https://youtu.be/GPCDungCTK8</t>
+  </si>
+  <si>
+    <t>PQ011</t>
+  </si>
+  <si>
+    <t>Close and Load</t>
+  </si>
+  <si>
+    <t>https://youtu.be/o1QVywo65fU</t>
   </si>
   <si>
     <t>2026-08-12</t>
   </si>
   <si>
-    <t>PQ006</t>
-  </si>
-  <si>
-    <t>Manage Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/7d6h1stqUVI</t>
-  </si>
-  <si>
-    <t>PQ007</t>
-  </si>
-  <si>
-    <t>Conditional Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/IIzoiGgQh9M</t>
-  </si>
-  <si>
-    <t>PQ008</t>
-  </si>
-  <si>
-    <t>Creating Index Columns</t>
-  </si>
-  <si>
-    <t>https://youtu.be/u4vHsVY6iWg</t>
-  </si>
-  <si>
-    <t>PQ009</t>
-  </si>
-  <si>
-    <t>Power Query Home Tab</t>
-  </si>
-  <si>
-    <t>https://youtu.be/y-g2-xv1wi4</t>
+    <t>PQ012</t>
+  </si>
+  <si>
+    <t>External Data Source (Web)</t>
+  </si>
+  <si>
+    <t>https://youtu.be/7PEovlMLfN4</t>
+  </si>
+  <si>
+    <t>PQ013</t>
+  </si>
+  <si>
+    <t>Merging Queries Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/53qoq8gTmEw</t>
+  </si>
+  <si>
+    <t>PQ014</t>
+  </si>
+  <si>
+    <t>Merging Queries Pt.2</t>
+  </si>
+  <si>
+    <t>https://youtu.be/rs1O1Q0AZrU</t>
+  </si>
+  <si>
+    <t>Excel Final Project</t>
+  </si>
+  <si>
+    <t>EX-RES088</t>
+  </si>
+  <si>
+    <t>Excel Final Project Dataset</t>
   </si>
   <si>
     <t>2026-08-13</t>
   </si>
   <si>
-    <t>PQ010</t>
-  </si>
-  <si>
-    <t>Power Query Transform Tab</t>
-  </si>
-  <si>
-    <t>https://youtu.be/GPCDungCTK8</t>
-  </si>
-  <si>
-    <t>PQ011</t>
-  </si>
-  <si>
-    <t>Close and Load</t>
-  </si>
-  <si>
-    <t>https://youtu.be/o1QVywo65fU</t>
-  </si>
-  <si>
-    <t>PQ012</t>
-  </si>
-  <si>
-    <t>External Data Source (Web)</t>
-  </si>
-  <si>
-    <t>https://youtu.be/7PEovlMLfN4</t>
-  </si>
-  <si>
-    <t>PQ013</t>
-  </si>
-  <si>
-    <t>Merging Queries Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/53qoq8gTmEw</t>
+    <t>EX-RES089</t>
+  </si>
+  <si>
+    <t>EX090</t>
+  </si>
+  <si>
+    <t>Data Protection</t>
+  </si>
+  <si>
+    <t>https://youtu.be/yRL09ge6UvY</t>
+  </si>
+  <si>
+    <t>EX091</t>
+  </si>
+  <si>
+    <t>https://youtu.be/i7Chd1Fne9k</t>
+  </si>
+  <si>
+    <t>EX092</t>
+  </si>
+  <si>
+    <t>Sharing Your Project</t>
+  </si>
+  <si>
+    <t>https://youtu.be/-2s7B3T4ZBw</t>
+  </si>
+  <si>
+    <t>EX093</t>
+  </si>
+  <si>
+    <t>Excel Add-ins</t>
+  </si>
+  <si>
+    <t>https://youtu.be/WLFAy_4rCvA</t>
+  </si>
+  <si>
+    <t>EX094</t>
+  </si>
+  <si>
+    <t>Final Project Pt.1</t>
+  </si>
+  <si>
+    <t>https://youtu.be/bjD7oT2h64Q</t>
   </si>
   <si>
     <t>2026-08-14</t>
   </si>
   <si>
-    <t>PQ014</t>
-  </si>
-  <si>
-    <t>Merging Queries Pt.2</t>
-  </si>
-  <si>
-    <t>https://youtu.be/rs1O1Q0AZrU</t>
-  </si>
-  <si>
-    <t>Excel Final Project</t>
-  </si>
-  <si>
-    <t>EX-RES088</t>
-  </si>
-  <si>
-    <t>Excel Final Project Dataset</t>
-  </si>
-  <si>
-    <t>EX-RES089</t>
-  </si>
-  <si>
-    <t>EX090</t>
-  </si>
-  <si>
-    <t>Data Protection</t>
-  </si>
-  <si>
-    <t>https://youtu.be/yRL09ge6UvY</t>
-  </si>
-  <si>
-    <t>EX091</t>
-  </si>
-  <si>
-    <t>https://youtu.be/i7Chd1Fne9k</t>
-  </si>
-  <si>
-    <t>EX092</t>
-  </si>
-  <si>
-    <t>Sharing Your Project</t>
-  </si>
-  <si>
-    <t>https://youtu.be/-2s7B3T4ZBw</t>
-  </si>
-  <si>
-    <t>2026-08-10</t>
-  </si>
-  <si>
-    <t>EX093</t>
-  </si>
-  <si>
-    <t>Excel Add-ins</t>
-  </si>
-  <si>
-    <t>https://youtu.be/WLFAy_4rCvA</t>
-  </si>
-  <si>
-    <t>EX094</t>
-  </si>
-  <si>
-    <t>Final Project Pt.1</t>
-  </si>
-  <si>
-    <t>https://youtu.be/bjD7oT2h64Q</t>
-  </si>
-  <si>
     <t>EX095</t>
   </si>
   <si>
@@ -1325,6 +1325,9 @@
     <t>https://youtu.be/Xa6ZHBx4l1Y</t>
   </si>
   <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
     <t>PB002</t>
   </si>
   <si>
@@ -1343,9 +1346,6 @@
     <t>https://youtu.be/ypbNYxOBEyQ</t>
   </si>
   <si>
-    <t>2026-08-17</t>
-  </si>
-  <si>
     <t>PB004</t>
   </si>
   <si>
@@ -1364,6 +1364,9 @@
     <t>https://youtu.be/U9sUno4v1tw</t>
   </si>
   <si>
+    <t>2026-08-18</t>
+  </si>
+  <si>
     <t>PB006</t>
   </si>
   <si>
@@ -1382,9 +1385,6 @@
     <t>https://youtu.be/HghrbUfyeTo</t>
   </si>
   <si>
-    <t>2026-08-18</t>
-  </si>
-  <si>
     <t>PB008</t>
   </si>
   <si>
@@ -1403,6 +1403,9 @@
     <t>https://youtu.be/etCykEN4MtM</t>
   </si>
   <si>
+    <t>2026-08-19</t>
+  </si>
+  <si>
     <t>PB010</t>
   </si>
   <si>
@@ -1424,9 +1427,6 @@
     <t>https://youtu.be/TwclhQBd0UY</t>
   </si>
   <si>
-    <t>2026-08-19</t>
-  </si>
-  <si>
     <t>PB012</t>
   </si>
   <si>
@@ -1445,6 +1445,9 @@
     <t>https://youtu.be/u74yveIYBbk</t>
   </si>
   <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
     <t>PB014</t>
   </si>
   <si>
@@ -1463,9 +1466,6 @@
     <t>https://youtu.be/OfPScKQn5vs</t>
   </si>
   <si>
-    <t>2026-08-20</t>
-  </si>
-  <si>
     <t>PB016</t>
   </si>
   <si>
@@ -1484,6 +1484,9 @@
     <t>https://youtu.be/2E9IvB4DIpk</t>
   </si>
   <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
     <t>PB018</t>
   </si>
   <si>
@@ -1502,9 +1505,6 @@
     <t>https://youtu.be/AaNi-sGOQB4</t>
   </si>
   <si>
-    <t>2026-08-21</t>
-  </si>
-  <si>
     <t>PB020</t>
   </si>
   <si>
@@ -1526,6 +1526,9 @@
     <t>https://youtu.be/MMgt3NOey8Y</t>
   </si>
   <si>
+    <t>2026-08-24</t>
+  </si>
+  <si>
     <t>PB022</t>
   </si>
   <si>
@@ -1544,9 +1547,6 @@
     <t>https://youtu.be/d7wg5gCd-5Q</t>
   </si>
   <si>
-    <t>2026-08-24</t>
-  </si>
-  <si>
     <t>PB024</t>
   </si>
   <si>
@@ -1565,6 +1565,9 @@
     <t>https://youtu.be/_H2BJ6Q9wdg</t>
   </si>
   <si>
+    <t>2026-08-25</t>
+  </si>
+  <si>
     <t>PB026</t>
   </si>
   <si>
@@ -1583,9 +1586,6 @@
     <t>https://youtu.be/mcuiS8CNBUU</t>
   </si>
   <si>
-    <t>2026-08-25</t>
-  </si>
-  <si>
     <t>PB028</t>
   </si>
   <si>
@@ -1613,6 +1613,9 @@
     <t>DateTable</t>
   </si>
   <si>
+    <t>2026-08-26</t>
+  </si>
+  <si>
     <t>PB-RES031</t>
   </si>
   <si>
@@ -1643,9 +1646,6 @@
     <t>https://youtu.be/sLD4dXCf-LQ</t>
   </si>
   <si>
-    <t>2026-08-26</t>
-  </si>
-  <si>
     <t>PB035</t>
   </si>
   <si>
@@ -1673,6 +1673,9 @@
     <t>https://youtu.be/58SuKknttOU</t>
   </si>
   <si>
+    <t>2026-08-27</t>
+  </si>
+  <si>
     <t>PB038</t>
   </si>
   <si>
@@ -1682,9 +1685,6 @@
     <t>https://youtu.be/hjwiy5TPoNY</t>
   </si>
   <si>
-    <t>2026-08-27</t>
-  </si>
-  <si>
     <t>PB039</t>
   </si>
   <si>
@@ -2223,9 +2223,6 @@
   </si>
   <si>
     <t>https://youtu.be/LZWTeYXzAO8</t>
-  </si>
-  <si>
-    <t>VERIFY LINK: current link appears to be SQL conclusion; original source did not include Python conclusion link.</t>
   </si>
   <si>
     <t>OVTech LMS Curriculum Fix Summary</t>
@@ -4283,7 +4280,7 @@
         <v>5</v>
       </c>
       <c r="K19" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" s="6" t="s">
         <v>83</v>
@@ -4327,7 +4324,7 @@
         <v>5</v>
       </c>
       <c r="K20" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="6" t="s">
         <v>83</v>
@@ -4371,7 +4368,7 @@
         <v>5</v>
       </c>
       <c r="K21" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="6" t="s">
         <v>83</v>
@@ -4415,7 +4412,7 @@
         <v>5</v>
       </c>
       <c r="K22" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>83</v>
@@ -4955,7 +4952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" ht="27.6" spans="1:14">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -4972,17 +4969,15 @@
         <v>18</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>134</v>
       </c>
       <c r="H35" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="5" t="s">
         <v>135</v>
       </c>
+      <c r="I35" s="5"/>
       <c r="J35" s="5">
         <v>8</v>
       </c>
@@ -4995,9 +4990,7 @@
       <c r="M35" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="N35" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="N35" s="6"/>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="5">
@@ -5028,16 +5021,16 @@
         <v>18</v>
       </c>
       <c r="J36" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K36" s="5">
         <v>2</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>18</v>
@@ -5054,7 +5047,7 @@
         <v>129</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E37" s="5">
         <v>20</v>
@@ -5063,10 +5056,10 @@
         <v>24</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>18</v>
@@ -5078,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>68</v>
@@ -5122,7 +5115,7 @@
         <v>2</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>68</v>
@@ -5166,7 +5159,7 @@
         <v>2</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>68</v>
@@ -5210,7 +5203,7 @@
         <v>2</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>68</v>
@@ -5251,7 +5244,7 @@
         <v>10</v>
       </c>
       <c r="K41" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="6" t="s">
         <v>155</v>
@@ -5295,7 +5288,7 @@
         <v>10</v>
       </c>
       <c r="K42" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L42" s="6" t="s">
         <v>155</v>
@@ -5339,7 +5332,7 @@
         <v>10</v>
       </c>
       <c r="K43" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" s="6" t="s">
         <v>155</v>
@@ -5383,7 +5376,7 @@
         <v>10</v>
       </c>
       <c r="K44" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" s="6" t="s">
         <v>155</v>
@@ -6263,7 +6256,7 @@
         <v>15</v>
       </c>
       <c r="K64" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L64" s="6" t="s">
         <v>229</v>
@@ -6307,7 +6300,7 @@
         <v>15</v>
       </c>
       <c r="K65" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L65" s="6" t="s">
         <v>229</v>
@@ -6351,7 +6344,7 @@
         <v>15</v>
       </c>
       <c r="K66" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L66" s="6" t="s">
         <v>229</v>
@@ -6395,7 +6388,7 @@
         <v>15</v>
       </c>
       <c r="K67" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L67" s="6" t="s">
         <v>229</v>
@@ -7143,7 +7136,7 @@
         <v>20</v>
       </c>
       <c r="K84" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L84" s="6" t="s">
         <v>291</v>
@@ -7187,7 +7180,7 @@
         <v>20</v>
       </c>
       <c r="K85" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L85" s="6" t="s">
         <v>291</v>
@@ -7231,7 +7224,7 @@
         <v>20</v>
       </c>
       <c r="K86" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L86" s="6" t="s">
         <v>291</v>
@@ -7275,7 +7268,7 @@
         <v>20</v>
       </c>
       <c r="K87" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L87" s="6" t="s">
         <v>291</v>
@@ -7319,7 +7312,7 @@
         <v>20</v>
       </c>
       <c r="K88" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L88" s="6" t="s">
         <v>291</v>
@@ -7363,7 +7356,7 @@
         <v>20</v>
       </c>
       <c r="K89" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L89" s="6" t="s">
         <v>291</v>
@@ -8064,7 +8057,7 @@
         <v>175</v>
       </c>
       <c r="J105" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K105" s="5">
         <v>6</v>
@@ -8073,7 +8066,7 @@
         <v>356</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N105" s="6" t="s">
         <v>22</v>
@@ -8108,7 +8101,7 @@
         <v>175</v>
       </c>
       <c r="J106" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K106" s="5">
         <v>6</v>
@@ -8117,7 +8110,7 @@
         <v>356</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N106" s="6" t="s">
         <v>22</v>
@@ -8152,7 +8145,7 @@
         <v>18</v>
       </c>
       <c r="J107" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K107" s="5">
         <v>6</v>
@@ -8161,7 +8154,7 @@
         <v>356</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N107" s="6" t="s">
         <v>18</v>
@@ -8196,7 +8189,7 @@
         <v>18</v>
       </c>
       <c r="J108" s="5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K108" s="5">
         <v>6</v>
@@ -8205,7 +8198,7 @@
         <v>356</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="N108" s="6" t="s">
         <v>18</v>
@@ -8240,16 +8233,16 @@
         <v>18</v>
       </c>
       <c r="J109" s="5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K109" s="5">
         <v>6</v>
       </c>
       <c r="L109" s="6" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="N109" s="6" t="s">
         <v>18</v>
@@ -8266,7 +8259,7 @@
         <v>353</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E110" s="5">
         <v>6</v>
@@ -8275,25 +8268,25 @@
         <v>24</v>
       </c>
       <c r="G110" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="H110" s="5" t="s">
         <v>370</v>
       </c>
-      <c r="H110" s="5" t="s">
-        <v>371</v>
-      </c>
       <c r="I110" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J110" s="5">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K110" s="5">
         <v>6</v>
       </c>
       <c r="L110" s="6" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="N110" s="6" t="s">
         <v>18</v>
@@ -8310,7 +8303,7 @@
         <v>353</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E111" s="5">
         <v>7</v>
@@ -8319,25 +8312,25 @@
         <v>24</v>
       </c>
       <c r="G111" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="H111" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="H111" s="5" t="s">
-        <v>374</v>
-      </c>
       <c r="I111" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J111" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K111" s="5">
         <v>6</v>
       </c>
       <c r="L111" s="6" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="N111" s="6" t="s">
         <v>18</v>
@@ -8372,16 +8365,16 @@
         <v>18</v>
       </c>
       <c r="J112" s="5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K112" s="5">
         <v>6</v>
       </c>
       <c r="L112" s="6" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="N112" s="6" t="s">
         <v>18</v>
@@ -8416,16 +8409,16 @@
         <v>18</v>
       </c>
       <c r="J113" s="5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K113" s="5">
         <v>6</v>
       </c>
       <c r="L113" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="N113" s="6" t="s">
         <v>18</v>
@@ -8442,7 +8435,7 @@
         <v>353</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E114" s="5">
         <v>10</v>
@@ -8451,25 +8444,25 @@
         <v>24</v>
       </c>
       <c r="G114" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H114" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="H114" s="5" t="s">
-        <v>384</v>
-      </c>
       <c r="I114" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J114" s="5">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="K114" s="5">
         <v>6</v>
       </c>
       <c r="L114" s="6" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="N114" s="6" t="s">
         <v>18</v>
@@ -8486,7 +8479,7 @@
         <v>353</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E115" s="5">
         <v>11</v>
@@ -8495,25 +8488,25 @@
         <v>24</v>
       </c>
       <c r="G115" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="H115" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="H115" s="5" t="s">
-        <v>387</v>
-      </c>
       <c r="I115" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J115" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K115" s="5">
         <v>6</v>
       </c>
       <c r="L115" s="6" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="N115" s="6" t="s">
         <v>18</v>
@@ -8548,16 +8541,16 @@
         <v>18</v>
       </c>
       <c r="J116" s="5">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K116" s="5">
         <v>6</v>
       </c>
       <c r="L116" s="6" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="N116" s="6" t="s">
         <v>18</v>
@@ -8592,16 +8585,16 @@
         <v>18</v>
       </c>
       <c r="J117" s="5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K117" s="5">
         <v>6</v>
       </c>
       <c r="L117" s="6" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="N117" s="6" t="s">
         <v>18</v>
@@ -8618,7 +8611,7 @@
         <v>353</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E118" s="5">
         <v>14</v>
@@ -8627,25 +8620,25 @@
         <v>24</v>
       </c>
       <c r="G118" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="H118" s="5" t="s">
         <v>396</v>
       </c>
-      <c r="H118" s="5" t="s">
-        <v>397</v>
-      </c>
       <c r="I118" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J118" s="5">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K118" s="5">
         <v>6</v>
       </c>
       <c r="L118" s="6" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>68</v>
+        <v>40</v>
       </c>
       <c r="N118" s="6" t="s">
         <v>18</v>
@@ -8659,10 +8652,10 @@
         <v>75</v>
       </c>
       <c r="C119" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="D119" s="5" t="s">
         <v>398</v>
-      </c>
-      <c r="D119" s="5" t="s">
-        <v>399</v>
       </c>
       <c r="E119" s="5">
         <v>88</v>
@@ -8671,7 +8664,7 @@
         <v>16</v>
       </c>
       <c r="G119" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H119" s="5" t="s">
         <v>18</v>
@@ -8680,16 +8673,16 @@
         <v>175</v>
       </c>
       <c r="J119" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K119" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L119" s="6" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="M119" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N119" s="6" t="s">
         <v>22</v>
@@ -8703,7 +8696,7 @@
         <v>75</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D120" s="5" t="s">
         <v>401</v>
@@ -8715,7 +8708,7 @@
         <v>16</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H120" s="5" t="s">
         <v>18</v>
@@ -8724,16 +8717,16 @@
         <v>132</v>
       </c>
       <c r="J120" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K120" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L120" s="6" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="M120" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N120" s="6" t="s">
         <v>22</v>
@@ -8747,7 +8740,7 @@
         <v>75</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D121" s="5" t="s">
         <v>402</v>
@@ -8768,16 +8761,16 @@
         <v>18</v>
       </c>
       <c r="J121" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K121" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L121" s="6" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="M121" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N121" s="6" t="s">
         <v>18</v>
@@ -8791,7 +8784,7 @@
         <v>75</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D122" s="5" t="s">
         <v>405</v>
@@ -8812,16 +8805,16 @@
         <v>18</v>
       </c>
       <c r="J122" s="5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K122" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L122" s="6" t="s">
-        <v>349</v>
+        <v>400</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N122" s="6" t="s">
         <v>18</v>
@@ -8835,7 +8828,7 @@
         <v>75</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D123" s="5" t="s">
         <v>407</v>
@@ -8856,16 +8849,16 @@
         <v>18</v>
       </c>
       <c r="J123" s="5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K123" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L123" s="6" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="M123" s="6" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="N123" s="6" t="s">
         <v>18</v>
@@ -8879,10 +8872,10 @@
         <v>75</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E124" s="5">
         <v>93</v>
@@ -8891,25 +8884,25 @@
         <v>24</v>
       </c>
       <c r="G124" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="H124" s="5" t="s">
         <v>412</v>
       </c>
-      <c r="H124" s="5" t="s">
-        <v>413</v>
-      </c>
       <c r="I124" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J124" s="5">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K124" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L124" s="6" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="N124" s="6" t="s">
         <v>18</v>
@@ -8923,10 +8916,10 @@
         <v>75</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E125" s="5">
         <v>94</v>
@@ -8935,25 +8928,25 @@
         <v>24</v>
       </c>
       <c r="G125" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="H125" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="H125" s="5" t="s">
+      <c r="I125" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J125" s="5">
+        <v>29</v>
+      </c>
+      <c r="K125" s="5">
+        <v>6</v>
+      </c>
+      <c r="L125" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="I125" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J125" s="5">
-        <v>25</v>
-      </c>
-      <c r="K125" s="5">
-        <v>5</v>
-      </c>
-      <c r="L125" s="6" t="s">
-        <v>410</v>
-      </c>
       <c r="M125" s="6" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N125" s="6" t="s">
         <v>18</v>
@@ -8967,7 +8960,7 @@
         <v>75</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>417</v>
@@ -8988,16 +8981,16 @@
         <v>18</v>
       </c>
       <c r="J126" s="5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K126" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L126" s="6" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N126" s="6" t="s">
         <v>18</v>
@@ -9011,7 +9004,7 @@
         <v>75</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D127" s="5" t="s">
         <v>420</v>
@@ -9032,16 +9025,16 @@
         <v>18</v>
       </c>
       <c r="J127" s="5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K127" s="5">
         <v>6</v>
       </c>
       <c r="L127" s="6" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="N127" s="6" t="s">
         <v>18</v>
@@ -9055,7 +9048,7 @@
         <v>75</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>423</v>
@@ -9076,16 +9069,16 @@
         <v>18</v>
       </c>
       <c r="J128" s="5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K128" s="5">
         <v>6</v>
       </c>
       <c r="L128" s="6" t="s">
-        <v>356</v>
+        <v>416</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="N128" s="6" t="s">
         <v>18</v>
@@ -9120,16 +9113,16 @@
         <v>18</v>
       </c>
       <c r="J129" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K129" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L129" s="6" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="M129" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N129" s="6" t="s">
         <v>18</v>
@@ -9146,7 +9139,7 @@
         <v>427</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E130" s="5">
         <v>2</v>
@@ -9155,25 +9148,25 @@
         <v>24</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H130" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="I130" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J130" s="5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K130" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L130" s="6" t="s">
-        <v>394</v>
+        <v>431</v>
       </c>
       <c r="M130" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N130" s="6" t="s">
         <v>18</v>
@@ -9190,7 +9183,7 @@
         <v>427</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="E131" s="5">
         <v>3</v>
@@ -9199,10 +9192,10 @@
         <v>24</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H131" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="I131" s="5" t="s">
         <v>18</v>
@@ -9211,10 +9204,10 @@
         <v>30</v>
       </c>
       <c r="K131" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L131" s="6" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="M131" s="6" t="s">
         <v>84</v>
@@ -9255,10 +9248,10 @@
         <v>30</v>
       </c>
       <c r="K132" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L132" s="6" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="M132" s="6" t="s">
         <v>84</v>
@@ -9296,16 +9289,16 @@
         <v>18</v>
       </c>
       <c r="J133" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K133" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L133" s="6" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="M133" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N133" s="6" t="s">
         <v>18</v>
@@ -9322,7 +9315,7 @@
         <v>427</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E134" s="5">
         <v>6</v>
@@ -9331,25 +9324,25 @@
         <v>24</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H134" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="I134" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J134" s="5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K134" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L134" s="6" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="M134" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N134" s="6" t="s">
         <v>18</v>
@@ -9366,7 +9359,7 @@
         <v>427</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E135" s="5">
         <v>7</v>
@@ -9375,10 +9368,10 @@
         <v>24</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I135" s="5" t="s">
         <v>18</v>
@@ -9390,7 +9383,7 @@
         <v>7</v>
       </c>
       <c r="L135" s="6" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="M135" s="6" t="s">
         <v>21</v>
@@ -9434,7 +9427,7 @@
         <v>7</v>
       </c>
       <c r="L136" s="6" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="M136" s="6" t="s">
         <v>21</v>
@@ -9478,10 +9471,10 @@
         <v>7</v>
       </c>
       <c r="L137" s="6" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="M137" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N137" s="6" t="s">
         <v>18</v>
@@ -9498,7 +9491,7 @@
         <v>427</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E138" s="5">
         <v>10</v>
@@ -9507,10 +9500,10 @@
         <v>24</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H138" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="I138" s="5" t="s">
         <v>18</v>
@@ -9522,10 +9515,10 @@
         <v>7</v>
       </c>
       <c r="L138" s="6" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="M138" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N138" s="6" t="s">
         <v>18</v>
@@ -9539,10 +9532,10 @@
         <v>426</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E139" s="5">
         <v>11</v>
@@ -9551,10 +9544,10 @@
         <v>24</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H139" s="5" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="I139" s="5" t="s">
         <v>18</v>
@@ -9566,7 +9559,7 @@
         <v>7</v>
       </c>
       <c r="L139" s="6" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="M139" s="6" t="s">
         <v>40</v>
@@ -9583,7 +9576,7 @@
         <v>426</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D140" s="5" t="s">
         <v>465</v>
@@ -9610,7 +9603,7 @@
         <v>7</v>
       </c>
       <c r="L140" s="6" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="M140" s="6" t="s">
         <v>40</v>
@@ -9627,7 +9620,7 @@
         <v>426</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D141" s="5" t="s">
         <v>468</v>
@@ -9654,10 +9647,10 @@
         <v>7</v>
       </c>
       <c r="L141" s="6" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="M141" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N141" s="6" t="s">
         <v>18</v>
@@ -9671,10 +9664,10 @@
         <v>426</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E142" s="5">
         <v>14</v>
@@ -9683,10 +9676,10 @@
         <v>24</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H142" s="5" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="I142" s="5" t="s">
         <v>18</v>
@@ -9698,10 +9691,10 @@
         <v>7</v>
       </c>
       <c r="L142" s="6" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="M142" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N142" s="6" t="s">
         <v>18</v>
@@ -9715,10 +9708,10 @@
         <v>426</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="E143" s="5">
         <v>15</v>
@@ -9727,10 +9720,10 @@
         <v>24</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H143" s="5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I143" s="5" t="s">
         <v>18</v>
@@ -9742,7 +9735,7 @@
         <v>7</v>
       </c>
       <c r="L143" s="6" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="M143" s="6" t="s">
         <v>54</v>
@@ -9759,7 +9752,7 @@
         <v>426</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>478</v>
@@ -9786,7 +9779,7 @@
         <v>7</v>
       </c>
       <c r="L144" s="6" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="M144" s="6" t="s">
         <v>54</v>
@@ -9803,7 +9796,7 @@
         <v>426</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D145" s="5" t="s">
         <v>481</v>
@@ -9830,10 +9823,10 @@
         <v>7</v>
       </c>
       <c r="L145" s="6" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="M145" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N145" s="6" t="s">
         <v>18</v>
@@ -9847,10 +9840,10 @@
         <v>426</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="E146" s="5">
         <v>18</v>
@@ -9859,10 +9852,10 @@
         <v>24</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H146" s="5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="I146" s="5" t="s">
         <v>18</v>
@@ -9874,10 +9867,10 @@
         <v>7</v>
       </c>
       <c r="L146" s="6" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="M146" s="6" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="N146" s="6" t="s">
         <v>18</v>
@@ -9891,10 +9884,10 @@
         <v>426</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="E147" s="5">
         <v>19</v>
@@ -9903,10 +9896,10 @@
         <v>24</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H147" s="5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I147" s="5" t="s">
         <v>18</v>
@@ -9918,7 +9911,7 @@
         <v>7</v>
       </c>
       <c r="L147" s="6" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="M147" s="6" t="s">
         <v>68</v>
@@ -9935,7 +9928,7 @@
         <v>426</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>491</v>
@@ -9962,7 +9955,7 @@
         <v>7</v>
       </c>
       <c r="L148" s="6" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="M148" s="6" t="s">
         <v>68</v>
@@ -10000,16 +9993,16 @@
         <v>18</v>
       </c>
       <c r="J149" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K149" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L149" s="6" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="M149" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N149" s="6" t="s">
         <v>18</v>
@@ -10026,7 +10019,7 @@
         <v>494</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="E150" s="5">
         <v>22</v>
@@ -10035,25 +10028,25 @@
         <v>24</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H150" s="5" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="I150" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J150" s="5">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K150" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L150" s="6" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="M150" s="6" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="N150" s="6" t="s">
         <v>18</v>
@@ -10070,7 +10063,7 @@
         <v>494</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="E151" s="5">
         <v>23</v>
@@ -10079,10 +10072,10 @@
         <v>24</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H151" s="5" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="I151" s="5" t="s">
         <v>18</v>
@@ -10091,10 +10084,10 @@
         <v>35</v>
       </c>
       <c r="K151" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L151" s="6" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M151" s="6" t="s">
         <v>84</v>
@@ -10135,10 +10128,10 @@
         <v>35</v>
       </c>
       <c r="K152" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L152" s="6" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M152" s="6" t="s">
         <v>84</v>
@@ -10176,16 +10169,16 @@
         <v>18</v>
       </c>
       <c r="J153" s="5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K153" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L153" s="6" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="M153" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N153" s="6" t="s">
         <v>18</v>
@@ -10202,7 +10195,7 @@
         <v>494</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E154" s="5">
         <v>26</v>
@@ -10211,10 +10204,10 @@
         <v>24</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H154" s="5" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="I154" s="5" t="s">
         <v>18</v>
@@ -10223,13 +10216,13 @@
         <v>35</v>
       </c>
       <c r="K154" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L154" s="6" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="M154" s="6" t="s">
-        <v>84</v>
+        <v>21</v>
       </c>
       <c r="N154" s="6" t="s">
         <v>18</v>
@@ -10246,7 +10239,7 @@
         <v>494</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E155" s="5">
         <v>27</v>
@@ -10255,10 +10248,10 @@
         <v>24</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="I155" s="5" t="s">
         <v>18</v>
@@ -10270,7 +10263,7 @@
         <v>8</v>
       </c>
       <c r="L155" s="6" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="M155" s="6" t="s">
         <v>21</v>
@@ -10314,7 +10307,7 @@
         <v>8</v>
       </c>
       <c r="L156" s="6" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="M156" s="6" t="s">
         <v>21</v>
@@ -10358,7 +10351,7 @@
         <v>8</v>
       </c>
       <c r="L157" s="6" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="M157" s="6" t="s">
         <v>21</v>
@@ -10396,16 +10389,16 @@
         <v>175</v>
       </c>
       <c r="J158" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K158" s="5">
         <v>8</v>
       </c>
       <c r="L158" s="6" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="M158" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N158" s="6" t="s">
         <v>22</v>
@@ -10422,7 +10415,7 @@
         <v>524</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E159" s="5">
         <v>31</v>
@@ -10431,7 +10424,7 @@
         <v>16</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H159" s="5" t="s">
         <v>18</v>
@@ -10440,16 +10433,16 @@
         <v>175</v>
       </c>
       <c r="J159" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K159" s="5">
         <v>8</v>
       </c>
       <c r="L159" s="6" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="M159" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N159" s="6" t="s">
         <v>22</v>
@@ -10466,7 +10459,7 @@
         <v>524</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="E160" s="5">
         <v>32</v>
@@ -10475,7 +10468,7 @@
         <v>16</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H160" s="5" t="s">
         <v>18</v>
@@ -10484,16 +10477,16 @@
         <v>175</v>
       </c>
       <c r="J160" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K160" s="5">
         <v>8</v>
       </c>
       <c r="L160" s="6" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="M160" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N160" s="6" t="s">
         <v>22</v>
@@ -10510,7 +10503,7 @@
         <v>524</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E161" s="5">
         <v>33</v>
@@ -10519,25 +10512,25 @@
         <v>24</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H161" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="I161" s="5" t="s">
         <v>18</v>
       </c>
       <c r="J161" s="5">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K161" s="5">
         <v>8</v>
       </c>
       <c r="L161" s="6" t="s">
-        <v>517</v>
+        <v>527</v>
       </c>
       <c r="M161" s="6" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N161" s="6" t="s">
         <v>18</v>
@@ -10554,7 +10547,7 @@
         <v>524</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E162" s="5">
         <v>34</v>
@@ -10563,10 +10556,10 @@
         <v>24</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H162" s="5" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="I162" s="5" t="s">
         <v>18</v>
@@ -10578,7 +10571,7 @@
         <v>8</v>
       </c>
       <c r="L162" s="6" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="M162" s="6" t="s">
         <v>40</v>
@@ -10622,7 +10615,7 @@
         <v>8</v>
       </c>
       <c r="L163" s="6" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="M163" s="6" t="s">
         <v>40</v>
@@ -10666,7 +10659,7 @@
         <v>8</v>
       </c>
       <c r="L164" s="6" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="M164" s="6" t="s">
         <v>40</v>
@@ -10704,16 +10697,16 @@
         <v>18</v>
       </c>
       <c r="J165" s="5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K165" s="5">
         <v>8</v>
       </c>
       <c r="L165" s="6" t="s">
-        <v>537</v>
+        <v>547</v>
       </c>
       <c r="M165" s="6" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="N165" s="6" t="s">
         <v>18</v>
@@ -10730,7 +10723,7 @@
         <v>524</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="E166" s="5">
         <v>38</v>
@@ -10739,10 +10732,10 @@
         <v>24</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H166" s="5" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="I166" s="5" t="s">
         <v>18</v>
@@ -10754,7 +10747,7 @@
         <v>8</v>
       </c>
       <c r="L166" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="M166" s="6" t="s">
         <v>54</v>
@@ -10798,7 +10791,7 @@
         <v>8</v>
       </c>
       <c r="L167" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="M167" s="6" t="s">
         <v>54</v>
@@ -10842,7 +10835,7 @@
         <v>8</v>
       </c>
       <c r="L168" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="M168" s="6" t="s">
         <v>54</v>
@@ -10886,7 +10879,7 @@
         <v>8</v>
       </c>
       <c r="L169" s="6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="M169" s="6" t="s">
         <v>54</v>
@@ -11103,7 +11096,7 @@
         <v>40</v>
       </c>
       <c r="K174" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L174" s="6" t="s">
         <v>575</v>
@@ -11147,7 +11140,7 @@
         <v>40</v>
       </c>
       <c r="K175" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L175" s="6" t="s">
         <v>575</v>
@@ -11191,7 +11184,7 @@
         <v>40</v>
       </c>
       <c r="K176" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L176" s="6" t="s">
         <v>575</v>
@@ -11235,7 +11228,7 @@
         <v>40</v>
       </c>
       <c r="K177" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L177" s="6" t="s">
         <v>575</v>
@@ -11279,7 +11272,7 @@
         <v>40</v>
       </c>
       <c r="K178" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L178" s="6" t="s">
         <v>575</v>
@@ -11323,7 +11316,7 @@
         <v>40</v>
       </c>
       <c r="K179" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L179" s="6" t="s">
         <v>575</v>
@@ -11367,7 +11360,7 @@
         <v>40</v>
       </c>
       <c r="K180" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L180" s="6" t="s">
         <v>575</v>
@@ -12115,7 +12108,7 @@
         <v>45</v>
       </c>
       <c r="K197" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L197" s="6" t="s">
         <v>643</v>
@@ -12159,7 +12152,7 @@
         <v>45</v>
       </c>
       <c r="K198" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L198" s="6" t="s">
         <v>643</v>
@@ -12203,7 +12196,7 @@
         <v>45</v>
       </c>
       <c r="K199" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L199" s="6" t="s">
         <v>643</v>
@@ -12247,7 +12240,7 @@
         <v>45</v>
       </c>
       <c r="K200" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L200" s="6" t="s">
         <v>643</v>
@@ -12995,7 +12988,7 @@
         <v>50</v>
       </c>
       <c r="K217" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L217" s="6" t="s">
         <v>709</v>
@@ -13039,7 +13032,7 @@
         <v>50</v>
       </c>
       <c r="K218" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L218" s="6" t="s">
         <v>709</v>
@@ -13083,7 +13076,7 @@
         <v>50</v>
       </c>
       <c r="K219" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L219" s="6" t="s">
         <v>709</v>
@@ -13127,7 +13120,7 @@
         <v>50</v>
       </c>
       <c r="K220" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L220" s="6" t="s">
         <v>709</v>
@@ -13311,13 +13304,11 @@
       <c r="M224" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="N224" s="6" t="s">
-        <v>731</v>
-      </c>
+      <c r="N224" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="F105 F106 F107 F108 F109 F110 F111 F112 F113 F114 F115 F116 F117 F118 F2:F104 F119:F128 F129:F224">
+    <dataValidation type="list" sqref="F2:F224">
       <formula1>"Video,Resource"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13346,24 +13337,24 @@
   <sheetData>
     <row r="1" ht="27.6" spans="1:4">
       <c r="A1" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>733</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>735</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>736</v>
       </c>
       <c r="C2" s="2">
         <v>15</v>
@@ -13374,7 +13365,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B3" s="2">
         <v>223</v>
@@ -13388,7 +13379,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B4" s="2">
         <v>204</v>
@@ -13402,7 +13393,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B5" s="2">
         <v>19</v>
@@ -13416,10 +13407,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>741</v>
       </c>
       <c r="C6" s="2">
         <v>28</v>
@@ -13430,10 +13421,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="C7" s="2">
         <v>20</v>
@@ -13444,15 +13435,15 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>744</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B9" s="2">
         <v>51</v>
@@ -13460,7 +13451,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>722</v>
@@ -13468,10 +13459,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>748</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -13531,50 +13522,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>750</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="2" ht="27.6" spans="1:2">
       <c r="A2" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>752</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>756</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="6" ht="27.6" spans="1:2">
       <c r="A6" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>758</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -13582,15 +13573,15 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>761</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>762</v>
       </c>
     </row>
   </sheetData>
@@ -13615,7 +13606,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -13627,15 +13618,15 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="2" ht="27.6" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>729</v>
@@ -13650,12 +13641,12 @@
         <v>664</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>23</v>
@@ -13670,12 +13661,12 @@
         <v>26</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>72</v>
@@ -13690,12 +13681,12 @@
         <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>88</v>
@@ -13710,12 +13701,12 @@
         <v>90</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
@@ -13730,12 +13721,12 @@
         <v>92</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>402</v>
@@ -13750,12 +13741,12 @@
         <v>404</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>405</v>
@@ -13770,7 +13761,7 @@
         <v>406</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="9" spans="1:6">
